--- a/data/mcct-dives.xlsx
+++ b/data/mcct-dives.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jacob/Documents/GitHub/vector-calculator/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jacob/Documents/GitHub/vector-calculator/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59A505C7-C04B-A94C-99C9-750052161A5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27C3BC20-250B-2747-9178-28B93884FADF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11360" yWindow="600" windowWidth="34500" windowHeight="19360" xr2:uid="{B0D2E8CF-998B-7740-9E47-F2272500F278}"/>
+    <workbookView xWindow="18100" yWindow="1240" windowWidth="34500" windowHeight="19360" xr2:uid="{B0D2E8CF-998B-7740-9E47-F2272500F278}"/>
   </bookViews>
   <sheets>
     <sheet name="mcct-dives" sheetId="1" r:id="rId1"/>
@@ -906,7 +906,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB81E609-636B-4146-B50E-86A5AE3BBBF2}">
-  <dimension ref="A1:G144"/>
+  <dimension ref="A1:G107"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="4" max="4" width="14" customWidth="1"/>
@@ -934,1121 +934,1121 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C2">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D2">
-        <v>521.31299999999999</v>
+        <v>586.64200000000005</v>
       </c>
       <c r="E2">
-        <v>135.5</v>
+        <v>37.200000000000003</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C3">
         <v>26</v>
       </c>
       <c r="D3">
-        <v>566.553</v>
+        <v>581.452</v>
       </c>
       <c r="E3">
-        <v>63.2</v>
+        <v>69.5</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B4">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C4">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D4">
-        <v>536.65599999999995</v>
+        <v>594.02300000000002</v>
       </c>
       <c r="E4">
-        <v>140.6</v>
+        <v>40.5</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B5">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C5">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D5">
-        <v>548.98299999999995</v>
+        <v>606.72900000000004</v>
       </c>
       <c r="E5">
-        <v>118.2</v>
+        <v>9.1999999999999993</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B6">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C6">
         <v>26</v>
       </c>
       <c r="D6">
-        <v>573.91200000000003</v>
+        <v>589.125</v>
       </c>
       <c r="E6">
-        <v>66.5</v>
+        <v>72.2</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B7">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C7">
         <v>27</v>
       </c>
       <c r="D7">
-        <v>586.64200000000005</v>
+        <v>601.58500000000004</v>
       </c>
       <c r="E7">
-        <v>37.200000000000003</v>
+        <v>43.5</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B8">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C8">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D8">
-        <v>545.57399999999996</v>
+        <v>614.10199999999998</v>
       </c>
       <c r="E8">
-        <v>142.69999999999999</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B9">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C9">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D9">
-        <v>557.80600000000004</v>
+        <v>626.80700000000002</v>
       </c>
       <c r="E9">
-        <v>120.6</v>
+        <v>-20.7</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B10">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C10">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D10">
-        <v>581.452</v>
+        <v>561.298</v>
       </c>
       <c r="E10">
-        <v>69.5</v>
+        <v>146</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B11">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C11">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D11">
-        <v>594.02300000000002</v>
+        <v>597.84699999999998</v>
       </c>
       <c r="E11">
-        <v>40.5</v>
+        <v>74.599999999999994</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B12">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C12">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D12">
-        <v>606.72900000000004</v>
+        <v>610.27800000000002</v>
       </c>
       <c r="E12">
-        <v>9.1999999999999993</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B13">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C13">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D13">
-        <v>553.46799999999996</v>
+        <v>622.69399999999996</v>
       </c>
       <c r="E13">
-        <v>144.5</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B14">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C14">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D14">
-        <v>565.51800000000003</v>
+        <v>634.17999999999995</v>
       </c>
       <c r="E14">
-        <v>122.7</v>
+        <v>-17.399999999999999</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B15">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C15">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D15">
-        <v>589.125</v>
+        <v>646.89</v>
       </c>
       <c r="E15">
-        <v>72.2</v>
+        <v>-52.7</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B16">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C16">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D16">
-        <v>601.58500000000004</v>
+        <v>569.44000000000005</v>
       </c>
       <c r="E16">
-        <v>43.5</v>
+        <v>147.19999999999999</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B17">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C17">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D17">
-        <v>614.10199999999998</v>
+        <v>593.41899999999998</v>
       </c>
       <c r="E17">
-        <v>12.5</v>
+        <v>102.5</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B18">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C18">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D18">
-        <v>626.80700000000002</v>
+        <v>605.71</v>
       </c>
       <c r="E18">
-        <v>-20.7</v>
+        <v>76.7</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B19">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C19">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D19">
-        <v>561.298</v>
+        <v>617.94899999999996</v>
       </c>
       <c r="E19">
-        <v>146</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B20">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C20">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D20">
-        <v>573.41</v>
+        <v>630.35500000000002</v>
       </c>
       <c r="E20">
-        <v>124.5</v>
+        <v>18.2</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B21">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C21">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D21">
-        <v>597.84699999999998</v>
+        <v>642.774</v>
       </c>
       <c r="E21">
-        <v>74.599999999999994</v>
+        <v>-14.4</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B22">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C22">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D22">
-        <v>610.27800000000002</v>
+        <v>654.25800000000004</v>
       </c>
       <c r="E22">
-        <v>46.2</v>
+        <v>-49.4</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B23">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C23">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D23">
-        <v>622.69399999999996</v>
+        <v>577.73199999999997</v>
       </c>
       <c r="E23">
-        <v>15.5</v>
+        <v>148.1</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B24">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C24">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D24">
-        <v>634.17999999999995</v>
+        <v>601.43499999999995</v>
       </c>
       <c r="E24">
-        <v>-17.399999999999999</v>
+        <v>104</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B25">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C25">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D25">
-        <v>646.89</v>
+        <v>613.57799999999997</v>
       </c>
       <c r="E25">
-        <v>-52.7</v>
+        <v>78.5</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B26">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C26">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D26">
-        <v>569.44000000000005</v>
+        <v>625.80600000000004</v>
       </c>
       <c r="E26">
-        <v>147.19999999999999</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A27">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B27">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C27">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D27">
-        <v>581.49</v>
+        <v>638.03200000000004</v>
       </c>
       <c r="E27">
-        <v>126</v>
+        <v>20.6</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B28">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C28">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D28">
-        <v>593.41899999999998</v>
+        <v>650.35</v>
       </c>
       <c r="E28">
-        <v>102.5</v>
+        <v>-11.7</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A29">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B29">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C29">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D29">
-        <v>605.71</v>
+        <v>662.84900000000005</v>
       </c>
       <c r="E29">
-        <v>76.7</v>
+        <v>-46.4</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A30">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B30">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C30">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D30">
-        <v>617.94899999999996</v>
+        <v>586.03899999999999</v>
       </c>
       <c r="E30">
-        <v>48.6</v>
+        <v>148.69999999999999</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A31">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B31">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C31">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D31">
-        <v>630.35500000000002</v>
+        <v>609.51900000000001</v>
       </c>
       <c r="E31">
-        <v>18.2</v>
+        <v>105.2</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A32">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B32">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C32">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D32">
-        <v>642.774</v>
+        <v>621.55799999999999</v>
       </c>
       <c r="E32">
-        <v>-14.4</v>
+        <v>80</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A33">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B33">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C33">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D33">
-        <v>654.25800000000004</v>
+        <v>633.66999999999996</v>
       </c>
       <c r="E33">
-        <v>-49.4</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A34">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B34">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C34">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D34">
-        <v>577.73199999999997</v>
+        <v>645.88699999999994</v>
       </c>
       <c r="E34">
-        <v>148.1</v>
+        <v>22.7</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A35">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B35">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C35">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D35">
-        <v>589.57000000000005</v>
+        <v>658.10799999999995</v>
       </c>
       <c r="E35">
-        <v>127.2</v>
+        <v>-9.3000000000000007</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A36">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B36">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C36">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D36">
-        <v>601.43499999999995</v>
+        <v>670.40499999999997</v>
       </c>
       <c r="E36">
-        <v>104</v>
+        <v>-43.7</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A37">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B37">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C37">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D37">
-        <v>613.57799999999997</v>
+        <v>594.36900000000003</v>
       </c>
       <c r="E37">
-        <v>78.5</v>
+        <v>149</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A38">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B38">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C38">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D38">
-        <v>625.80600000000004</v>
+        <v>617.72299999999996</v>
       </c>
       <c r="E38">
-        <v>50.7</v>
+        <v>106.1</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A39">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B39">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C39">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D39">
-        <v>638.03200000000004</v>
+        <v>629.63599999999997</v>
       </c>
       <c r="E39">
-        <v>20.6</v>
+        <v>81.2</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A40">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B40">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C40">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D40">
-        <v>650.35</v>
+        <v>641.64700000000005</v>
       </c>
       <c r="E40">
-        <v>-11.7</v>
+        <v>54</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A41">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B41">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C41">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D41">
-        <v>662.84900000000005</v>
+        <v>653.75</v>
       </c>
       <c r="E41">
-        <v>-46.4</v>
+        <v>24.5</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A42">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B42">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C42">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D42">
-        <v>586.03899999999999</v>
+        <v>665.87099999999998</v>
       </c>
       <c r="E42">
-        <v>148.69999999999999</v>
+        <v>-7.2</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A43">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B43">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C43">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D43">
-        <v>597.76400000000001</v>
+        <v>602.88699999999994</v>
       </c>
       <c r="E43">
-        <v>128.1</v>
+        <v>149</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A44">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B44">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C44">
         <v>25</v>
       </c>
       <c r="D44">
-        <v>609.51900000000001</v>
+        <v>626.03399999999999</v>
       </c>
       <c r="E44">
-        <v>105.2</v>
+        <v>106.7</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A45">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B45">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C45">
         <v>26</v>
       </c>
       <c r="D45">
-        <v>621.55799999999999</v>
+        <v>637.81299999999999</v>
       </c>
       <c r="E45">
-        <v>80</v>
+        <v>82.1</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A46">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B46">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C46">
         <v>27</v>
       </c>
       <c r="D46">
-        <v>633.66999999999996</v>
+        <v>649.721</v>
       </c>
       <c r="E46">
-        <v>52.5</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A47">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B47">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C47">
         <v>28</v>
       </c>
       <c r="D47">
-        <v>645.88699999999994</v>
+        <v>661.72199999999998</v>
       </c>
       <c r="E47">
-        <v>22.7</v>
+        <v>26</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A48">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B48">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C48">
         <v>29</v>
       </c>
       <c r="D48">
-        <v>658.10799999999995</v>
+        <v>673.82600000000002</v>
       </c>
       <c r="E48">
-        <v>-9.3000000000000007</v>
+        <v>-5.4</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A49">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B49">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="C49">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="D49">
-        <v>670.40499999999997</v>
+        <v>611.50800000000004</v>
       </c>
       <c r="E49">
-        <v>-43.7</v>
+        <v>148.69999999999999</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A50">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B50">
         <v>19</v>
       </c>
       <c r="C50">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D50">
-        <v>594.36900000000003</v>
+        <v>634.39</v>
       </c>
       <c r="E50">
-        <v>149</v>
+        <v>107</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A51">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B51">
         <v>18</v>
       </c>
       <c r="C51">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D51">
-        <v>606.05200000000002</v>
+        <v>646.11500000000001</v>
       </c>
       <c r="E51">
-        <v>128.69999999999999</v>
+        <v>82.7</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A52">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B52">
         <v>17</v>
       </c>
       <c r="C52">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D52">
-        <v>617.72299999999996</v>
+        <v>657.89200000000005</v>
       </c>
       <c r="E52">
-        <v>106.1</v>
+        <v>56.1</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A53">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B53">
         <v>16</v>
       </c>
       <c r="C53">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D53">
-        <v>629.63599999999997</v>
+        <v>669.79899999999998</v>
       </c>
       <c r="E53">
-        <v>81.2</v>
+        <v>27.2</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A54">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B54">
         <v>15</v>
       </c>
       <c r="C54">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D54">
-        <v>641.64700000000005</v>
+        <v>681.79899999999998</v>
       </c>
       <c r="E54">
-        <v>54</v>
+        <v>-3.9</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A55">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B55">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C55">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D55">
-        <v>653.75</v>
+        <v>620.24099999999999</v>
       </c>
       <c r="E55">
-        <v>24.5</v>
+        <v>148.1</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A56">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B56">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="C56">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D56">
-        <v>665.87099999999998</v>
+        <v>642.90700000000004</v>
       </c>
       <c r="E56">
-        <v>-7.2</v>
+        <v>107</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A57">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B57">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C57">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D57">
-        <v>602.88699999999994</v>
+        <v>654.52</v>
       </c>
       <c r="E57">
-        <v>149</v>
+        <v>83</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A58">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B58">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C58">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D58">
-        <v>614.45399999999995</v>
+        <v>666.18200000000002</v>
       </c>
       <c r="E58">
-        <v>129</v>
+        <v>56.7</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A59">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B59">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C59">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D59">
-        <v>626.03399999999999</v>
+        <v>677.97</v>
       </c>
       <c r="E59">
-        <v>106.7</v>
+        <v>28.1</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A60">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B60">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C60">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D60">
-        <v>637.81299999999999</v>
+        <v>689.86500000000001</v>
       </c>
       <c r="E60">
-        <v>82.1</v>
+        <v>-2.7</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A61">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B61">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C61">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D61">
-        <v>649.721</v>
+        <v>629.01599999999996</v>
       </c>
       <c r="E61">
-        <v>55.2</v>
+        <v>147.19999999999999</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A62">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B62">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C62">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D62">
-        <v>661.72199999999998</v>
+        <v>663.00199999999995</v>
       </c>
       <c r="E62">
-        <v>26</v>
+        <v>83</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A63">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B63">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C63">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D63">
-        <v>673.82600000000002</v>
+        <v>674.57</v>
       </c>
       <c r="E63">
-        <v>-5.4</v>
+        <v>57</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A64">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B64">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C64">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D64">
-        <v>611.50800000000004</v>
+        <v>686.25199999999995</v>
       </c>
       <c r="E64">
-        <v>148.69999999999999</v>
+        <v>28.7</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A65">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B65">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C65">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D65">
-        <v>622.95799999999997</v>
+        <v>698.03700000000003</v>
       </c>
       <c r="E65">
-        <v>129</v>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A66">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B66">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C66">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D66">
-        <v>634.39</v>
+        <v>637.91700000000003</v>
       </c>
       <c r="E66">
-        <v>107</v>
+        <v>146</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A67">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B67">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C67">
         <v>26</v>
       </c>
       <c r="D67">
-        <v>646.11500000000001</v>
+        <v>671.625</v>
       </c>
       <c r="E67">
         <v>82.7</v>
@@ -2056,1317 +2056,688 @@
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A68">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B68">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C68">
         <v>27</v>
       </c>
       <c r="D68">
-        <v>657.89200000000005</v>
+        <v>683.08100000000002</v>
       </c>
       <c r="E68">
-        <v>56.1</v>
+        <v>57</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A69">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B69">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C69">
         <v>28</v>
       </c>
       <c r="D69">
-        <v>669.79899999999998</v>
+        <v>694.65</v>
       </c>
       <c r="E69">
-        <v>27.2</v>
+        <v>29</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A70">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B70">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C70">
         <v>29</v>
       </c>
       <c r="D70">
-        <v>681.79899999999998</v>
+        <v>705.93600000000004</v>
       </c>
       <c r="E70">
-        <v>-3.9</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A71">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B71">
+        <v>26</v>
+      </c>
+      <c r="C71">
         <v>22</v>
       </c>
-      <c r="C71">
-        <v>23</v>
-      </c>
       <c r="D71">
-        <v>620.24099999999999</v>
+        <v>637.03800000000001</v>
       </c>
       <c r="E71">
-        <v>148.1</v>
+        <v>157.1</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A72">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B72">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C72">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D72">
-        <v>631.49699999999996</v>
+        <v>647.23199999999997</v>
       </c>
       <c r="E72">
-        <v>128.69999999999999</v>
+        <v>143.30000000000001</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A73">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B73">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C73">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D73">
-        <v>642.90700000000004</v>
+        <v>680.28</v>
       </c>
       <c r="E73">
-        <v>107</v>
+        <v>82.1</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A74">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B74">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C74">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D74">
-        <v>654.52</v>
+        <v>691.697</v>
       </c>
       <c r="E74">
-        <v>83</v>
+        <v>56.7</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A75">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B75">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C75">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D75">
-        <v>666.18200000000002</v>
+        <v>703.13900000000001</v>
       </c>
       <c r="E75">
-        <v>56.7</v>
+        <v>29</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A76">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B76">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="C76">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D76">
-        <v>677.97</v>
+        <v>637.005</v>
       </c>
       <c r="E76">
-        <v>28.1</v>
+        <v>160.19999999999999</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A77">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B77">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="C77">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="D77">
-        <v>689.86500000000001</v>
+        <v>647.19799999999998</v>
       </c>
       <c r="E77">
-        <v>-2.7</v>
+        <v>151.4</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A78">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B78">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C78">
         <v>23</v>
       </c>
       <c r="D78">
-        <v>629.01599999999996</v>
+        <v>657.03899999999999</v>
       </c>
       <c r="E78">
-        <v>147.19999999999999</v>
+        <v>139.1</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A79">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B79">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C79">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D79">
-        <v>640.22199999999998</v>
+        <v>675.86199999999997</v>
       </c>
       <c r="E79">
-        <v>128.1</v>
+        <v>104</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A80">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B80">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C80">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D80">
-        <v>651.529</v>
+        <v>689.12699999999995</v>
       </c>
       <c r="E80">
-        <v>106.7</v>
+        <v>81.2</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A81">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B81">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C81">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D81">
-        <v>663.00199999999995</v>
+        <v>700.27800000000002</v>
       </c>
       <c r="E81">
-        <v>83</v>
+        <v>56.1</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A82">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B82">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C82">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D82">
-        <v>674.57</v>
+        <v>711.67200000000003</v>
       </c>
       <c r="E82">
-        <v>57</v>
+        <v>28.7</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A83">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B83">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C83">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="D83">
-        <v>686.25199999999995</v>
+        <v>637.66300000000001</v>
       </c>
       <c r="E83">
-        <v>28.7</v>
+        <v>155.30000000000001</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A84">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B84">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="C84">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="D84">
-        <v>698.03700000000003</v>
+        <v>647.78200000000004</v>
       </c>
       <c r="E84">
-        <v>-1.8</v>
+        <v>151.5</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A85">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B85">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C85">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D85">
-        <v>637.91700000000003</v>
+        <v>657.44399999999996</v>
       </c>
       <c r="E85">
-        <v>146</v>
+        <v>144.19999999999999</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A86">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B86">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C86">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D86">
-        <v>648.98900000000003</v>
+        <v>687.27499999999998</v>
       </c>
       <c r="E86">
-        <v>127.2</v>
+        <v>101.3</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A87">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B87">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C87">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D87">
-        <v>660.17600000000004</v>
+        <v>697.95699999999999</v>
       </c>
       <c r="E87">
-        <v>106.1</v>
+        <v>80</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A88">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B88">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C88">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D88">
-        <v>671.625</v>
+        <v>709.11900000000003</v>
       </c>
       <c r="E88">
-        <v>82.7</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A89">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B89">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C89">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D89">
-        <v>683.08100000000002</v>
+        <v>720.32399999999996</v>
       </c>
       <c r="E89">
-        <v>57</v>
+        <v>28.1</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A90">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B90">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="C90">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="D90">
-        <v>694.65</v>
+        <v>648.41</v>
       </c>
       <c r="E90">
-        <v>29</v>
+        <v>143.6</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A91">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B91">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C91">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="D91">
-        <v>706.28300000000002</v>
+        <v>658.02200000000005</v>
       </c>
       <c r="E91">
-        <v>-1.2</v>
+        <v>141.30000000000001</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A92">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B92">
+        <v>25</v>
+      </c>
+      <c r="C92">
         <v>26</v>
       </c>
-      <c r="C92">
-        <v>22</v>
-      </c>
       <c r="D92">
-        <v>637.03800000000001</v>
+        <v>707.303</v>
       </c>
       <c r="E92">
-        <v>157.1</v>
+        <v>77.3</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A93">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B93">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C93">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D93">
-        <v>647.23199999999997</v>
+        <v>718.02</v>
       </c>
       <c r="E93">
-        <v>143.30000000000001</v>
+        <v>54</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A94">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B94">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C94">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D94">
-        <v>657.94399999999996</v>
+        <v>729.18</v>
       </c>
       <c r="E94">
-        <v>126</v>
+        <v>27.2</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A95">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B95">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C95">
         <v>26</v>
       </c>
       <c r="D95">
-        <v>680.28</v>
+        <v>717.07600000000002</v>
       </c>
       <c r="E95">
-        <v>82.1</v>
+        <v>73.099999999999994</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A96">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B96">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C96">
         <v>27</v>
       </c>
       <c r="D96">
-        <v>691.697</v>
+        <v>727.36599999999999</v>
       </c>
       <c r="E96">
-        <v>56.7</v>
+        <v>51.3</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A97">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B97">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C97">
         <v>28</v>
       </c>
       <c r="D97">
-        <v>703.13900000000001</v>
+        <v>737.49199999999996</v>
       </c>
       <c r="E97">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A98">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B98">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="C98">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="D98">
-        <v>714.673</v>
+        <v>669.21799999999996</v>
       </c>
       <c r="E98">
-        <v>-0.9</v>
+        <v>115.7</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A99">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B99">
         <v>28</v>
       </c>
       <c r="C99">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D99">
-        <v>637.005</v>
+        <v>716.94600000000003</v>
       </c>
       <c r="E99">
-        <v>160.19999999999999</v>
+        <v>84.2</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A100">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B100">
+        <v>26</v>
+      </c>
+      <c r="C100">
         <v>27</v>
       </c>
-      <c r="C100">
-        <v>22</v>
-      </c>
       <c r="D100">
-        <v>647.19799999999998</v>
+        <v>737.125</v>
       </c>
       <c r="E100">
-        <v>151.4</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A101">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="B101">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="C101">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D101">
-        <v>657.03899999999999</v>
+        <v>689.31799999999998</v>
       </c>
       <c r="E101">
-        <v>139.1</v>
+        <v>101.7</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A102">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="B102">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C102">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D102">
-        <v>667.19799999999998</v>
+        <v>737.56700000000001</v>
       </c>
       <c r="E102">
-        <v>123.3</v>
+        <v>60.2</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A103">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="B103">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C103">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D103">
-        <v>675.86199999999997</v>
+        <v>742.46199999999999</v>
       </c>
       <c r="E103">
-        <v>104</v>
+        <v>41.4</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A104">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="B104">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="C104">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D104">
-        <v>689.12699999999995</v>
+        <v>709.41200000000003</v>
       </c>
       <c r="E104">
-        <v>81.2</v>
+        <v>85.7</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A105">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="B105">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="C105">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D105">
-        <v>700.27800000000002</v>
+        <v>734.38400000000001</v>
       </c>
       <c r="E105">
-        <v>56.1</v>
+        <v>65.3</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A106">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B106">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="C106">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D106">
-        <v>711.67200000000003</v>
+        <v>729.46900000000005</v>
       </c>
       <c r="E106">
-        <v>28.7</v>
+        <v>67.7</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A107">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="B107">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="C107">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="D107">
-        <v>723.16300000000001</v>
+        <v>746.82399999999996</v>
       </c>
       <c r="E107">
-        <v>-0.9</v>
-      </c>
-    </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A108">
-        <v>50</v>
-      </c>
-      <c r="B108">
-        <v>30</v>
-      </c>
-      <c r="C108">
-        <v>20</v>
-      </c>
-      <c r="D108">
-        <v>637.66300000000001</v>
-      </c>
-      <c r="E108">
-        <v>155.30000000000001</v>
-      </c>
-    </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A109">
-        <v>50</v>
-      </c>
-      <c r="B109">
-        <v>29</v>
-      </c>
-      <c r="C109">
-        <v>21</v>
-      </c>
-      <c r="D109">
-        <v>647.78200000000004</v>
-      </c>
-      <c r="E109">
-        <v>151.5</v>
-      </c>
-    </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A110">
-        <v>50</v>
-      </c>
-      <c r="B110">
-        <v>28</v>
-      </c>
-      <c r="C110">
-        <v>22</v>
-      </c>
-      <c r="D110">
-        <v>657.44399999999996</v>
-      </c>
-      <c r="E110">
-        <v>144.19999999999999</v>
-      </c>
-    </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A111">
-        <v>50</v>
-      </c>
-      <c r="B111">
-        <v>27</v>
-      </c>
-      <c r="C111">
-        <v>23</v>
-      </c>
-      <c r="D111">
-        <v>667.15700000000004</v>
-      </c>
-      <c r="E111">
-        <v>133.4</v>
-      </c>
-    </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A112">
-        <v>50</v>
-      </c>
-      <c r="B112">
-        <v>26</v>
-      </c>
-      <c r="C112">
-        <v>24</v>
-      </c>
-      <c r="D112">
-        <v>676.99</v>
-      </c>
-      <c r="E112">
-        <v>119.1</v>
-      </c>
-    </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A113">
-        <v>50</v>
-      </c>
-      <c r="B113">
-        <v>25</v>
-      </c>
-      <c r="C113">
-        <v>25</v>
-      </c>
-      <c r="D113">
-        <v>687.27499999999998</v>
-      </c>
-      <c r="E113">
-        <v>101.3</v>
-      </c>
-    </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A114">
-        <v>50</v>
-      </c>
-      <c r="B114">
-        <v>24</v>
-      </c>
-      <c r="C114">
-        <v>26</v>
-      </c>
-      <c r="D114">
-        <v>697.95699999999999</v>
-      </c>
-      <c r="E114">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A115">
-        <v>50</v>
-      </c>
-      <c r="B115">
-        <v>23</v>
-      </c>
-      <c r="C115">
-        <v>27</v>
-      </c>
-      <c r="D115">
-        <v>709.11900000000003</v>
-      </c>
-      <c r="E115">
-        <v>55.2</v>
-      </c>
-    </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A116">
-        <v>50</v>
-      </c>
-      <c r="B116">
-        <v>22</v>
-      </c>
-      <c r="C116">
-        <v>28</v>
-      </c>
-      <c r="D116">
-        <v>720.32399999999996</v>
-      </c>
-      <c r="E116">
-        <v>28.1</v>
-      </c>
-    </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A117">
-        <v>50</v>
-      </c>
-      <c r="B117">
-        <v>21</v>
-      </c>
-      <c r="C117">
-        <v>29</v>
-      </c>
-      <c r="D117">
-        <v>730.63499999999999</v>
-      </c>
-      <c r="E117">
-        <v>-1.2</v>
-      </c>
-    </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A118">
-        <v>51</v>
-      </c>
-      <c r="B118">
-        <v>31</v>
-      </c>
-      <c r="C118">
-        <v>20</v>
-      </c>
-      <c r="D118">
-        <v>648.41</v>
-      </c>
-      <c r="E118">
-        <v>143.6</v>
-      </c>
-    </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A119">
-        <v>51</v>
-      </c>
-      <c r="B119">
-        <v>30</v>
-      </c>
-      <c r="C119">
-        <v>21</v>
-      </c>
-      <c r="D119">
-        <v>658.02200000000005</v>
-      </c>
-      <c r="E119">
-        <v>141.30000000000001</v>
-      </c>
-    </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A120">
-        <v>51</v>
-      </c>
-      <c r="B120">
-        <v>29</v>
-      </c>
-      <c r="C120">
-        <v>22</v>
-      </c>
-      <c r="D120">
-        <v>667.74599999999998</v>
-      </c>
-      <c r="E120">
-        <v>135.5</v>
-      </c>
-    </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A121">
-        <v>51</v>
-      </c>
-      <c r="B121">
-        <v>28</v>
-      </c>
-      <c r="C121">
-        <v>23</v>
-      </c>
-      <c r="D121">
-        <v>677.46900000000005</v>
-      </c>
-      <c r="E121">
-        <v>126.2</v>
-      </c>
-    </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A122">
-        <v>51</v>
-      </c>
-      <c r="B122">
-        <v>27</v>
-      </c>
-      <c r="C122">
-        <v>24</v>
-      </c>
-      <c r="D122">
-        <v>687.21900000000005</v>
-      </c>
-      <c r="E122">
-        <v>113.4</v>
-      </c>
-    </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A123">
-        <v>51</v>
-      </c>
-      <c r="B123">
-        <v>25</v>
-      </c>
-      <c r="C123">
-        <v>26</v>
-      </c>
-      <c r="D123">
-        <v>707.303</v>
-      </c>
-      <c r="E123">
-        <v>77.3</v>
-      </c>
-    </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A124">
-        <v>51</v>
-      </c>
-      <c r="B124">
-        <v>24</v>
-      </c>
-      <c r="C124">
-        <v>27</v>
-      </c>
-      <c r="D124">
-        <v>718.02</v>
-      </c>
-      <c r="E124">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A125">
-        <v>51</v>
-      </c>
-      <c r="B125">
-        <v>23</v>
-      </c>
-      <c r="C125">
-        <v>28</v>
-      </c>
-      <c r="D125">
-        <v>729.18</v>
-      </c>
-      <c r="E125">
-        <v>27.2</v>
-      </c>
-    </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A126">
-        <v>52</v>
-      </c>
-      <c r="B126">
-        <v>32</v>
-      </c>
-      <c r="C126">
-        <v>20</v>
-      </c>
-      <c r="D126">
-        <v>658.851</v>
-      </c>
-      <c r="E126">
-        <v>130.4</v>
-      </c>
-    </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A127">
-        <v>52</v>
-      </c>
-      <c r="B127">
-        <v>31</v>
-      </c>
-      <c r="C127">
-        <v>21</v>
-      </c>
-      <c r="D127">
-        <v>668.43200000000002</v>
-      </c>
-      <c r="E127">
-        <v>129.6</v>
-      </c>
-    </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A128">
-        <v>52</v>
-      </c>
-      <c r="B128">
-        <v>30</v>
-      </c>
-      <c r="C128">
-        <v>22</v>
-      </c>
-      <c r="D128">
-        <v>678.05600000000004</v>
-      </c>
-      <c r="E128">
-        <v>125.3</v>
-      </c>
-    </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A129">
-        <v>52</v>
-      </c>
-      <c r="B129">
-        <v>29</v>
-      </c>
-      <c r="C129">
-        <v>23</v>
-      </c>
-      <c r="D129">
-        <v>687.75400000000002</v>
-      </c>
-      <c r="E129">
-        <v>117.5</v>
-      </c>
-    </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A130">
-        <v>52</v>
-      </c>
-      <c r="B130">
-        <v>26</v>
-      </c>
-      <c r="C130">
-        <v>26</v>
-      </c>
-      <c r="D130">
-        <v>717.07600000000002</v>
-      </c>
-      <c r="E130">
-        <v>73.099999999999994</v>
-      </c>
-    </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A131">
-        <v>52</v>
-      </c>
-      <c r="B131">
-        <v>25</v>
-      </c>
-      <c r="C131">
-        <v>27</v>
-      </c>
-      <c r="D131">
-        <v>727.36599999999999</v>
-      </c>
-      <c r="E131">
-        <v>51.3</v>
-      </c>
-    </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A132">
-        <v>52</v>
-      </c>
-      <c r="B132">
-        <v>24</v>
-      </c>
-      <c r="C132">
-        <v>28</v>
-      </c>
-      <c r="D132">
-        <v>737.40099999999995</v>
-      </c>
-      <c r="E132">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A133">
-        <v>53</v>
-      </c>
-      <c r="B133">
-        <v>33</v>
-      </c>
-      <c r="C133">
-        <v>20</v>
-      </c>
-      <c r="D133">
-        <v>669.21799999999996</v>
-      </c>
-      <c r="E133">
-        <v>115.7</v>
-      </c>
-    </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A134">
-        <v>53</v>
-      </c>
-      <c r="B134">
-        <v>32</v>
-      </c>
-      <c r="C134">
-        <v>21</v>
-      </c>
-      <c r="D134">
-        <v>678.82299999999998</v>
-      </c>
-      <c r="E134">
-        <v>116.4</v>
-      </c>
-    </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A135">
-        <v>53</v>
-      </c>
-      <c r="B135">
-        <v>31</v>
-      </c>
-      <c r="C135">
-        <v>22</v>
-      </c>
-      <c r="D135">
-        <v>688.40800000000002</v>
-      </c>
-      <c r="E135">
-        <v>113.6</v>
-      </c>
-    </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A136">
-        <v>53</v>
-      </c>
-      <c r="B136">
-        <v>28</v>
-      </c>
-      <c r="C136">
-        <v>25</v>
-      </c>
-      <c r="D136">
-        <v>716.94600000000003</v>
-      </c>
-      <c r="E136">
-        <v>84.2</v>
-      </c>
-    </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A137">
-        <v>53</v>
-      </c>
-      <c r="B137">
-        <v>26</v>
-      </c>
-      <c r="C137">
-        <v>27</v>
-      </c>
-      <c r="D137">
-        <v>737.125</v>
-      </c>
-      <c r="E137">
-        <v>47.1</v>
-      </c>
-    </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A138">
-        <v>54</v>
-      </c>
-      <c r="B138">
-        <v>33</v>
-      </c>
-      <c r="C138">
-        <v>21</v>
-      </c>
-      <c r="D138">
-        <v>689.31799999999998</v>
-      </c>
-      <c r="E138">
-        <v>101.7</v>
-      </c>
-    </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A139">
-        <v>54</v>
-      </c>
-      <c r="B139">
-        <v>28</v>
-      </c>
-      <c r="C139">
-        <v>26</v>
-      </c>
-      <c r="D139">
-        <v>737.56700000000001</v>
-      </c>
-      <c r="E139">
-        <v>60.2</v>
-      </c>
-    </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A140">
-        <v>54</v>
-      </c>
-      <c r="B140">
-        <v>27</v>
-      </c>
-      <c r="C140">
-        <v>27</v>
-      </c>
-      <c r="D140">
-        <v>742.46199999999999</v>
-      </c>
-      <c r="E140">
-        <v>41.4</v>
-      </c>
-    </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A141">
-        <v>55</v>
-      </c>
-      <c r="B141">
-        <v>33</v>
-      </c>
-      <c r="C141">
-        <v>22</v>
-      </c>
-      <c r="D141">
-        <v>709.41200000000003</v>
-      </c>
-      <c r="E141">
-        <v>85.7</v>
-      </c>
-    </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A142">
-        <v>55</v>
-      </c>
-      <c r="B142">
-        <v>30</v>
-      </c>
-      <c r="C142">
-        <v>25</v>
-      </c>
-      <c r="D142">
-        <v>734.38400000000001</v>
-      </c>
-      <c r="E142">
-        <v>65.3</v>
-      </c>
-    </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A143">
-        <v>56</v>
-      </c>
-      <c r="B143">
-        <v>33</v>
-      </c>
-      <c r="C143">
-        <v>23</v>
-      </c>
-      <c r="D143">
-        <v>729.46900000000005</v>
-      </c>
-      <c r="E143">
-        <v>67.7</v>
-      </c>
-    </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A144">
-        <v>57</v>
-      </c>
-      <c r="B144">
-        <v>33</v>
-      </c>
-      <c r="C144">
-        <v>24</v>
-      </c>
-      <c r="D144">
-        <v>746.82399999999996</v>
-      </c>
-      <c r="E144">
         <v>47.7</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E144">
-    <sortCondition ref="A2:A144"/>
-    <sortCondition ref="D2:D144"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E107">
+    <sortCondition ref="A2:A107"/>
+    <sortCondition ref="D2:D107"/>
   </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
